--- a/output/第10期計画素案_修正指示書_令和8年8月.xlsx
+++ b/output/第10期計画素案_修正指示書_令和8年8月.xlsx
@@ -632,13 +632,13 @@
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>② 施策の空白5領域を
+          <t>② 調査に所見があるが対応する施策を確認できない5領域を
 　　明らかにした</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>調査に明確な所見があるのに第9期の施策体系に対応する施策がない領域が5つある（移動・交通、経済的理由による未利用、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけ）。第10期の施策体系の設計はここから始める。</t>
+          <t>調査に明確な所見があるのに第9期の施策体系に対応する施策がない領域が5つある（移動・交通、未利用の理由の把握、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけ）。第10期の施策体系の設計はここから始める。</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>移動・交通、経済的理由による未利用、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけの5領域を「第10期の施策の空白」として表に整理した。</t>
+          <t>移動・交通、未利用の理由の把握、人生の最終段階における意思決定支援、身寄りのない高齢者、未利用認定者への働きかけの5領域を「調査に所見があるが対応する施策を確認できない領域」として表に整理した。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>「評価できない施策の存在」（5施策）と「施策の空白」（5領域）を主要課題に加えた。</t>
+          <t>「評価できない施策の存在」（5施策）と「調査に所見があるが対応する施策を確認できない領域」（5領域）を主要課題に加えた。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>19施策の評価表、施策の空白5領域、主要課題</t>
+          <t>19施策の評価表、調査に所見があるが対応する施策を確認できない5領域、主要課題</t>
         </is>
       </c>
       <c r="G20" s="10" t="n"/>
@@ -1554,7 +1554,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>【2　施策の空白5領域】</t>
+          <t>【2　調査に所見があるが対応する施策を確認できない5領域】</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>経済的な理由による未利用</t>
+          <t>未利用の理由の把握</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>注3）5領域のうち④（身寄りのない高齢者）のみ、第10期の施策として位置づける案を示した。他の4領域は、広域連合の計画で扱うか3町の計画で扱うかの決定を要する［要協議］。注4）②（経済的な理由による未利用）は、未利用の要因のうち経済的理由が占める割合が確定していない。504人の要因の分解は第10期の中心論点である。</t>
+          <t>注3）5領域のうち④（身寄りのない高齢者）のみ、第10期の施策として位置づける案を示した。他の4領域は、広域連合の計画で扱うか3町の計画で扱うかの決定を要する［要協議］。注4）②（未利用の理由の把握）は、未利用の要因のうち経済的理由が占める割合が確定していない。504人の要因の分解は第10期の中心論点である。</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>判定「なし」の5施策について、指標の新設又は統合を定める。施策の空白5領域について、広域連合の計画で扱うか3町の計画で扱うかを定める。</t>
+          <t>判定「なし」の5施策について、指標の新設又は統合を定める。調査に所見があるが対応する施策を確認できない5領域について、広域連合の計画で扱うか3町の計画で扱うかを定める。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n"/>
@@ -3554,7 +3554,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>注1）作業①は資料の受領を待たずに着手できる。判定「なし」の5施策と施策の空白5領域の扱いは、データではなく方針の決定によるためである。注2）作業②が本業務の最大の未了事項である。資料No.1は令和8年8月14日時点で未受領であり、最優先で依頼している。注3）作業⑤は計画本文の修正ではなく、別管理表の確認事項B No.5に対する受託者の案の見直しである。</t>
+          <t>注1）作業①は資料の受領を待たずに着手できる。判定「なし」の5施策と調査に所見があるが対応する施策を確認できない5領域の扱いは、データではなく方針の決定によるためである。注2）作業②が本業務の最大の未了事項である。資料No.1は令和8年8月14日時点で未受領であり、最優先で依頼している。注3）作業⑤は計画本文の修正ではなく、別管理表の確認事項B No.5に対する受託者の案の見直しである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画素案_修正指示書_令和8年8月.xlsx
+++ b/output/第10期計画素案_修正指示書_令和8年8月.xlsx
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>介護サービス利用率74.3％（平成28年度82.2％から7.9ポイント低下）。全国平均の39.2％にとどまる</t>
+          <t>介護サービス利用率74.3％（平成28年度82.2％から7.9ポイント低下）。交付金評価の「アウトリーチ等の取組状況」の得点が全国平均比39.2％</t>
         </is>
       </c>
       <c r="D19" s="10" t="n"/>
